--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:15</t>
+    <t xml:space="preserve">2026-09-09 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:14</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -883,34 +883,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>18.43</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20.73</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>19.62</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15.11</v>
+        <v>19.62</v>
       </c>
     </row>
   </sheetData>
@@ -943,134 +943,134 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>18.43</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>17.71</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15.05</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20.73</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>19.84</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>18.91</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>19.62</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18.88</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>18.07</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>15.11</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>14.34</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="14">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -604,7 +604,7 @@
         <v>-1.02</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5.94</v>
+        <v>-5.97</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -627,7 +627,7 @@
         <v>-0.66</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3.51</v>
+        <v>-3.52</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
@@ -6,75 +6,56 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Barras" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Provincias" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mapa" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sexo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sexo'!$A$1:$D$6</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subgrupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_prev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prov_rank</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t xml:space="preserve">Unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente a la region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente al anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Región del Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
-    <t xml:space="preserve">Femenino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masculino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promedio Regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:38</t>
+    <t xml:space="preserve">2026-09-28 21:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -92,13 +73,13 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">% bajo 50% de la mediana</t>
+    <t xml:space="preserve">I_perINGR_MEDIAN_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Maule</t>
+    <t xml:space="preserve">Región de Maule</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -107,16 +88,13 @@
     <t xml:space="preserve">2022</t>
   </si>
   <si>
-    <t xml:space="preserve">ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_hist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brecha de las mujeres</t>
   </si>
 </sst>
 </file>
@@ -481,13 +459,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,288 +482,76 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>18.1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>18.04</v>
+        <v>18.8</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="n">
-        <v>5</v>
+      <c r="E2" s="2" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="n">
+        <v>2.6</v>
+      </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>20.76</v>
-      </c>
+      <c r="B5" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>4</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>16.14</v>
-      </c>
+      <c r="B6" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="2" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>18.78</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-3.52</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="E6" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -804,58 +568,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -869,8 +633,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,236 +644,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15.11</v>
+        <v>20.8</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18.43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>20.73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>19.62</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B5"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>15.11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14.34</v>
+        <v>19.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>32</v>
+      <c r="B4" s="2" t="n">
+        <v>22.9</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14</v>
+        <v>17.2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>20.3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>18.43</v>
+        <v>16.9</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17.71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>15.05</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>20.73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>19.84</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>18.91</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>19.62</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>18.88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>18.07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>18.12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>17.32</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>16.6</v>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_maule.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:39</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
